--- a/data/trans_orig/P42-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P42-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2007</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2007 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>268</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275983</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>265757</t>
+          <t>264596</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285801</t>
+          <t>285096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>275983</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>265757</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>285801</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>86,99%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>93,55%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29530</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>20417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39756</t>
+          <t>40917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>29530</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>19712</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>39756</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>13,01%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>297</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>305513</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>305513</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>305513</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>305513</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>305513</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>305513</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>315209</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300824</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>328135</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>301507</t>
+          <t>300824</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>328495</t>
+          <t>328135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>315209</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>301507</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>328495</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>85,43%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>81,72%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>89,03%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53741</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40455</t>
+          <t>40815</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67443</t>
+          <t>68126</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>53741</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>40455</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>67443</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>18,28%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>361</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>368950</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>368950</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>368950</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>368950</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>368950</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>368950</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141052</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149569</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130165</t>
+          <t>130585</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149745</t>
+          <t>149569</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>141052</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>130165</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>149745</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>89,25%</t>
+          <t>89,14%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26730</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37197</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37617</t>
+          <t>37197</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>26730</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>18037</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>37617</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>164</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167782</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167782</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>552</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568575</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>548235</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>591912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>546048</t>
+          <t>548235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>590533</t>
+          <t>591912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>568575</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>546048</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>590533</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>80,04%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>76,87%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>83,13%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141761</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118424</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162101</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119803</t>
+          <t>118424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164288</t>
+          <t>162101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>141761</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>119803</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>164288</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>16,87%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>23,13%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>690</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>710336</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>710336</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>710336</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>710336</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>710336</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>710336</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2095,37 +1615,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>451</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474826</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>458253</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>491828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>456329</t>
+          <t>458253</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>490953</t>
+          <t>491828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>474826</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>456329</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>490953</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>84,23%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>80,95%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>87,09%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -2208,37 +1693,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88885</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71883</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105458</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72758</t>
+          <t>71883</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107382</t>
+          <t>105458</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>88885</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>72758</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>107382</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>12,91%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>19,05%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -2321,37 +1771,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>535</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>563711</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>563711</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>563711</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2385,41 +1835,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>563711</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>563711</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>563711</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2438,37 +1853,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>867</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>884639</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>855894</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>915274</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>848820</t>
+          <t>855894</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>914034</t>
+          <t>915274</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,47 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>884639</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>848820</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>914034</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>68,08%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>73,31%</t>
+          <t>73,41%</t>
         </is>
       </c>
     </row>
@@ -2551,37 +1931,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>369</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>362094</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>331459</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>390839</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332699</t>
+          <t>331459</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>390839</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,47 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>362094</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>332699</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>397913</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>26,69%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>31,92%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -2664,37 +2009,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1246733</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1246733</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1246733</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2728,41 +2073,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1246733</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1246733</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1246733</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2781,37 +2091,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2660283</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2613629</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2705541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2608201</t>
+          <t>2613629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2703420</t>
+          <t>2705541</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,47 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2583</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2660283</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>2608201</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2703420</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>79,1%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>77,56%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>80,39%</t>
+          <t>80,45%</t>
         </is>
       </c>
     </row>
@@ -2894,37 +2169,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>702743</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>657485</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>749397</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>659606</t>
+          <t>657485</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>754825</t>
+          <t>749397</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,47 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>702743</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>659606</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>754825</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>20,9%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>19,61%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>22,44%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -3007,37 +2247,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3363026</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3363026</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3363026</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3071,41 +2311,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3283</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3363026</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3363026</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3363026</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3119,7 +2324,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3127,7 +2332,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -3142,7 +2346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3161,25 +2365,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2012</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2012 (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3190,7 +2387,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3199,17 +2396,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3280,41 +2466,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3337,13 +2488,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3358,37 +2502,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>273</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>303002</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>293427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +2547,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>293735</t>
+          <t>293427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>308924</t>
+          <t>308642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,47 +2562,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>303002</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>293735</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>308924</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>93,41%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -3471,37 +2580,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +2625,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20719</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,47 +2640,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>11452</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>5530</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>20719</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -3584,37 +2658,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3648,41 +2722,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>314454</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>314454</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>314454</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3701,37 +2740,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>315195</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>305161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>323152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +2785,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>304757</t>
+          <t>305161</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>322301</t>
+          <t>323152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,47 +2800,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>315195</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>304757</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>322301</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>91,08%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -3814,37 +2818,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19415</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +2863,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29853</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,47 +2878,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>19415</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>12309</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>29853</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -3927,37 +2896,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>302</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334610</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334610</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3991,41 +2960,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>334610</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>334610</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>334610</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4044,37 +2978,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>226</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239910</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>229479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>247872</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>229359</t>
+          <t>229479</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>247187</t>
+          <t>247872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,47 +3038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>239910</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>229359</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>247187</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>92,6%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>88,53%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -4157,37 +3056,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3101,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29726</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,47 +3116,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>19175</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>11898</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>29726</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -4270,37 +3134,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>259085</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>259085</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>259085</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4334,41 +3198,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>259085</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>259085</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>259085</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4387,37 +3216,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>632</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683397</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>666182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>699341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +3261,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>666200</t>
+          <t>666182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>699874</t>
+          <t>699341</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,42 +3281,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>683397</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>666200</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>699874</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>89,63%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>87,37%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>91,79%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -4500,37 +3294,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79087</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63143</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96302</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +3339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62610</t>
+          <t>63143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96284</t>
+          <t>96302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,45 +3354,10 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>79087</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>62610</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>96284</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>12,63%</t>
         </is>
@@ -4613,37 +3372,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>707</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>762484</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>762484</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>762484</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4677,41 +3436,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>762484</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>762484</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>762484</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4730,37 +3454,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>613</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>665085</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>644217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>681718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +3499,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>644993</t>
+          <t>644217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>682143</t>
+          <t>681718</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,47 +3514,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>665085</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>644993</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>682143</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>88,08%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>85,42%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>90,34%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>
@@ -4843,37 +3532,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89991</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +3577,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72933</t>
+          <t>73358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110083</t>
+          <t>110859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,47 +3592,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>89991</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>72933</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>110083</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -4956,37 +3610,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>697</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>755076</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>755076</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>755076</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5020,41 +3674,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>755076</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>755076</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>755076</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5073,37 +3692,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>814</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>870451</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>840694</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>896358</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +3737,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>842023</t>
+          <t>840694</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>898162</t>
+          <t>896358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,47 +3752,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>870451</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>842023</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>898162</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>76,25%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>81,34%</t>
+          <t>81,17%</t>
         </is>
       </c>
     </row>
@@ -5186,37 +3770,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>233819</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207912</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>263576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +3815,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>206108</t>
+          <t>207912</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262247</t>
+          <t>263576</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,47 +3830,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>233819</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>206108</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>262247</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>21,17%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>18,66%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>23,75%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -5299,37 +3848,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1104270</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1104270</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1104270</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5363,41 +3912,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1104270</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1104270</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1104270</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5416,37 +3930,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3077041</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3034061</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3115281</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +3975,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3036310</t>
+          <t>3034061</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3114759</t>
+          <t>3115281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,47 +3990,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2841</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>3077041</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>3036310</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3114759</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>88,24%</t>
+          <t>88,25%</t>
         </is>
       </c>
     </row>
@@ -5529,37 +4008,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>430</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>452938</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414698</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>495918</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +4053,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>415220</t>
+          <t>414698</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>493669</t>
+          <t>495918</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,47 +4068,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>452938</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>415220</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>493669</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -5642,37 +4086,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3529979</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3529979</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3529979</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5706,41 +4150,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3271</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3529979</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3529979</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3529979</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5754,7 +4163,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5762,7 +4171,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -5777,7 +4185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5796,25 +4204,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2016</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2016 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5825,7 +4226,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5834,17 +4235,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5915,41 +4305,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5972,13 +4327,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5993,37 +4341,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>313</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>327276</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>316885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333794</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +4386,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>315715</t>
+          <t>316885</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>333716</t>
+          <t>333794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,47 +4401,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>327276</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>315715</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>333716</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>91,4%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -6106,37 +4419,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28547</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +4464,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29717</t>
+          <t>28547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,47 +4479,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>18156</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>11716</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>29717</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -6219,37 +4497,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>331</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>345432</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>345432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>345432</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6283,41 +4561,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>345432</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>345432</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>345432</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6336,37 +4579,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353348</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>359835</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +4624,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>343923</t>
+          <t>344160</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>359988</t>
+          <t>359835</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,47 +4639,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>353348</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>343923</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>359988</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>93,25%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -6449,37 +4657,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15456</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +4702,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>24644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,47 +4717,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>15456</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>8816</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>24881</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -6562,37 +4735,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>349</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>368804</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>368804</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>368804</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6626,41 +4799,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>368804</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>368804</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>368804</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6679,37 +4817,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>142</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155576</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>160536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +4862,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>147909</t>
+          <t>148031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160752</t>
+          <t>160536</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,47 +4877,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>155576</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>147909</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>160752</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>89,04%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -6792,37 +4895,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18092</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +4940,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>18092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,47 +4955,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>10547</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>5371</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>18214</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -6905,37 +4973,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>153</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6969,41 +5037,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7022,37 +5055,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>715</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>741854</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>724621</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>760503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +5100,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>722667</t>
+          <t>724621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>756942</t>
+          <t>760503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,47 +5115,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>741854</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>722667</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>756942</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>90,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>87,83%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>91,99%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -7135,37 +5133,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80984</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62335</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +5178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65896</t>
+          <t>62335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100171</t>
+          <t>98217</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,47 +5193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>80984</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>65896</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>100171</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -7248,37 +5211,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>795</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>822838</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>822838</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>822838</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7312,41 +5275,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>822838</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>822838</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>822838</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7365,37 +5293,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>606</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>639538</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>621181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>656675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +5338,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>621283</t>
+          <t>621181</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>656786</t>
+          <t>656675</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,47 +5353,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>639538</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>621283</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>656786</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>85,03%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>89,89%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -7478,37 +5371,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91129</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +5416,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73881</t>
+          <t>73992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109384</t>
+          <t>109486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,47 +5431,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>91129</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>73881</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>109384</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>14,97%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -7591,37 +5449,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>692</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>730667</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>730667</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>730667</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7655,41 +5513,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>730667</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>730667</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>730667</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7708,37 +5531,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>761</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>836918</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>806954</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>861913</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +5576,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>808745</t>
+          <t>806954</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>862568</t>
+          <t>861913</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,47 +5591,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>836918</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>808745</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>862568</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>78,2%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>75,56%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>80,59%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -7821,37 +5609,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>220</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>233367</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>208372</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>263331</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +5654,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207717</t>
+          <t>208372</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261540</t>
+          <t>263331</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,47 +5669,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>233367</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>207717</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>261540</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>21,8%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -7934,37 +5687,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>981</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1070285</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1070285</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1070285</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7998,41 +5751,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>981</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1070285</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1070285</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1070285</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8051,37 +5769,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3054509</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3014640</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3095158</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +5814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3018221</t>
+          <t>3014640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3097426</t>
+          <t>3095158</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,47 +5829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2871</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>3054509</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>3018221</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3097426</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>86,13%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>88,39%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -8164,37 +5847,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>430</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449639</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>408990</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>489508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +5892,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>406722</t>
+          <t>408990</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>485927</t>
+          <t>489508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,47 +5907,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>449639</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>406722</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>485927</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>13,87%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -8277,37 +5925,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3504148</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3504148</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3504148</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8341,41 +5989,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3504148</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3504148</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3504148</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8389,7 +6002,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8397,7 +6010,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -8412,7 +6024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8431,25 +6043,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2023</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2023 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8460,7 +6065,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8469,17 +6074,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -8550,41 +6144,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -8607,13 +6166,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -8628,37 +6180,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>277514</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267599</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>287158</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +6225,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>266957</t>
+          <t>267599</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286462</t>
+          <t>287158</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,47 +6240,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>277514</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>266957</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>286462</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>90,45%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>87,01%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -8741,37 +6258,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39216</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +6303,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39858</t>
+          <t>39216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,47 +6318,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>29301</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>20353</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>39858</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>12,99%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -8854,37 +6336,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>476</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>306815</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>306815</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>306815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8918,41 +6400,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>306815</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>306815</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>306815</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8971,37 +6418,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>397</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>249452</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239328</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>256975</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239222</t>
+          <t>239328</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>257702</t>
+          <t>256975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,47 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>249452</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>239222</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>257702</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>90,34%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>86,63%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -9084,37 +6496,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26689</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +6541,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36919</t>
+          <t>36813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,47 +6556,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>26689</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>18439</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>36919</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -9197,37 +6574,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>276141</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>276141</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>276141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9261,41 +6638,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>276141</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>276141</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>276141</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9314,37 +6656,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>178</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102148</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94961</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +6701,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94996</t>
+          <t>94961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107903</t>
+          <t>108057</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,47 +6716,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>102148</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>94996</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>107903</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>86,02%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>80,0%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>90,87%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -9427,37 +6734,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +6779,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,47 +6794,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>16602</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>10847</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>23754</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -9540,37 +6812,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118750</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118750</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9604,41 +6876,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>118750</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>118750</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>118750</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9657,37 +6894,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>788</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>489849</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>677276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +6939,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>203767</t>
+          <t>222771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>676202</t>
+          <t>677276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,47 +6954,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>489849</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>203767</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>676202</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>64,31%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>26,75%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>88,77%</t>
+          <t>88,91%</t>
         </is>
       </c>
     </row>
@@ -9770,37 +6972,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271906</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>538984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +7017,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85553</t>
+          <t>84479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>557988</t>
+          <t>538984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,47 +7032,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>271906</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>85553</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>557988</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>35,69%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>73,25%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -9883,37 +7050,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>879</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>761755</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>761755</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>761755</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9947,41 +7114,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>761755</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>761755</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>761755</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10000,37 +7132,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>868</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>599860</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>580001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>625050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +7177,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>580870</t>
+          <t>580001</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>622497</t>
+          <t>625050</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,47 +7192,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>599860</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>580870</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>622497</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>85,13%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -10113,37 +7210,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82510</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57320</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +7255,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59873</t>
+          <t>57320</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101500</t>
+          <t>102369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,47 +7270,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>82510</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>59873</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>101500</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -10226,37 +7288,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>682370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>682370</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>682370</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10290,41 +7352,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>682370</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>682370</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>682370</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10343,37 +7370,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>780</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>454503</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>428890</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>479000</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +7415,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>429933</t>
+          <t>428890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>478605</t>
+          <t>479000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,47 +7430,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>454503</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>429933</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>478605</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>73,67%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>69,69%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
+          <t>77,65%</t>
         </is>
       </c>
     </row>
@@ -10456,37 +7448,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162402</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>137905</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188015</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +7493,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138300</t>
+          <t>137905</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186972</t>
+          <t>188015</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,47 +7508,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>162402</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>138300</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>186972</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>26,33%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>30,31%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -10569,37 +7526,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>931</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>616905</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>616905</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>616905</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10633,41 +7590,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>616905</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>616905</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>616905</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10686,37 +7608,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2173326</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1734975</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2365160</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +7653,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1655621</t>
+          <t>1734975</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2357236</t>
+          <t>2365160</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,47 +7668,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3449</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2173326</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1655621</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2357236</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>78,67%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>59,93%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>85,32%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -10799,37 +7686,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>494</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>589411</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>397577</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1027762</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +7731,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>405501</t>
+          <t>397577</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1107116</t>
+          <t>1027762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,47 +7746,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>589411</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>405501</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1107116</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>21,33%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>40,07%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -10912,37 +7764,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2762737</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2762737</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2762737</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10976,41 +7828,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3943</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2762737</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>2762737</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2762737</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11024,7 +7841,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11032,7 +7849,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>

--- a/data/trans_orig/P42-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P42-Clase-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>264596</t>
+          <t>263465</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>285096</t>
+          <t>284840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>264596</t>
+          <t>263465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285096</t>
+          <t>284840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>20673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40917</t>
+          <t>42048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>20673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40917</t>
+          <t>42048</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>300824</t>
+          <t>300657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>328135</t>
+          <t>327577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>300824</t>
+          <t>300657</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>328135</t>
+          <t>327577</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40815</t>
+          <t>41373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68126</t>
+          <t>68293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40815</t>
+          <t>41373</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68126</t>
+          <t>68293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130585</t>
+          <t>130313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149569</t>
+          <t>149939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130585</t>
+          <t>130313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149569</t>
+          <t>149939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37197</t>
+          <t>37469</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37197</t>
+          <t>37469</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>548235</t>
+          <t>546740</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>591912</t>
+          <t>586952</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>548235</t>
+          <t>546740</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>591912</t>
+          <t>586952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>118424</t>
+          <t>123384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162101</t>
+          <t>163596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118424</t>
+          <t>123384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162101</t>
+          <t>163596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>458253</t>
+          <t>455999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>491828</t>
+          <t>491901</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>458253</t>
+          <t>455999</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>491828</t>
+          <t>491901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71883</t>
+          <t>71810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105458</t>
+          <t>107712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71883</t>
+          <t>71810</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105458</t>
+          <t>107712</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>855894</t>
+          <t>854616</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>915274</t>
+          <t>917978</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>855894</t>
+          <t>854616</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>915274</t>
+          <t>917978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>331459</t>
+          <t>328755</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>390839</t>
+          <t>392117</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>331459</t>
+          <t>328755</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>390839</t>
+          <t>392117</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2613629</t>
+          <t>2612929</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2705541</t>
+          <t>2704967</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2613629</t>
+          <t>2612929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2705541</t>
+          <t>2704967</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,43%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>657485</t>
+          <t>658059</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>749397</t>
+          <t>750097</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>657485</t>
+          <t>658059</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>749397</t>
+          <t>750097</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>293427</t>
+          <t>293528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>308642</t>
+          <t>308508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>293427</t>
+          <t>293528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>308642</t>
+          <t>308508</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21027</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21027</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>305161</t>
+          <t>304131</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>323152</t>
+          <t>322072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>305161</t>
+          <t>304131</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>323152</t>
+          <t>322072</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -2828,12 +2828,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29449</t>
+          <t>30479</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29449</t>
+          <t>30479</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>229479</t>
+          <t>230098</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>247872</t>
+          <t>247696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>229479</t>
+          <t>230098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>247872</t>
+          <t>247696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>28987</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>28987</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>666182</t>
+          <t>664498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>699341</t>
+          <t>698837</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>666182</t>
+          <t>664498</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>699341</t>
+          <t>698837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63143</t>
+          <t>63647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96302</t>
+          <t>97986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63143</t>
+          <t>63647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96302</t>
+          <t>97986</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>644217</t>
+          <t>646507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>681718</t>
+          <t>681956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>644217</t>
+          <t>646507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>681718</t>
+          <t>681956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73358</t>
+          <t>73120</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110859</t>
+          <t>108569</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73358</t>
+          <t>73120</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110859</t>
+          <t>108569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>840694</t>
+          <t>842536</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>896358</t>
+          <t>896818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>840694</t>
+          <t>842536</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>896358</t>
+          <t>896818</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207912</t>
+          <t>207452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263576</t>
+          <t>261734</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207912</t>
+          <t>207452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263576</t>
+          <t>261734</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3034061</t>
+          <t>3037764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3115281</t>
+          <t>3116516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3034061</t>
+          <t>3037764</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3115281</t>
+          <t>3116516</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -4018,12 +4018,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>414698</t>
+          <t>413463</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>495918</t>
+          <t>492215</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>414698</t>
+          <t>413463</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>495918</t>
+          <t>492215</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>316885</t>
+          <t>318474</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>333794</t>
+          <t>334543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>316885</t>
+          <t>318474</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>333794</t>
+          <t>334543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4429,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>344160</t>
+          <t>343212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>359835</t>
+          <t>359522</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>344160</t>
+          <t>343212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>359835</t>
+          <t>359522</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4667,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24644</t>
+          <t>25592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24644</t>
+          <t>25592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>148031</t>
+          <t>148003</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160536</t>
+          <t>160835</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148031</t>
+          <t>148003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160536</t>
+          <t>160835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4905,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18092</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18092</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -5065,12 +5065,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>724621</t>
+          <t>723124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>760503</t>
+          <t>756898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>724621</t>
+          <t>723124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>760503</t>
+          <t>756898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62335</t>
+          <t>65940</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98217</t>
+          <t>99714</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62335</t>
+          <t>65940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98217</t>
+          <t>99714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>621181</t>
+          <t>621154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>656675</t>
+          <t>657174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>621181</t>
+          <t>621154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>656675</t>
+          <t>657174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,94%</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73992</t>
+          <t>73493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109486</t>
+          <t>109513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73992</t>
+          <t>73493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109486</t>
+          <t>109513</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>806954</t>
+          <t>806961</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>861913</t>
+          <t>863187</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>806954</t>
+          <t>806961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>861913</t>
+          <t>863187</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208372</t>
+          <t>207098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263331</t>
+          <t>263324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208372</t>
+          <t>207098</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263331</t>
+          <t>263324</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3014640</t>
+          <t>3012935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3095158</t>
+          <t>3095017</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3014640</t>
+          <t>3012935</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3095158</t>
+          <t>3095017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>408990</t>
+          <t>409131</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>489508</t>
+          <t>491213</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>408990</t>
+          <t>409131</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>489508</t>
+          <t>491213</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -6185,32 +6185,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>277514</t>
+          <t>303164</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>267599</t>
+          <t>291229</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>287158</t>
+          <t>312589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6220,32 +6220,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>277514</t>
+          <t>303164</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>267599</t>
+          <t>291229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287158</t>
+          <t>312589</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -6263,32 +6263,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19657</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39216</t>
+          <t>45081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6298,32 +6298,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19657</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39216</t>
+          <t>45081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6341,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>306815</t>
+          <t>336310</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>306815</t>
+          <t>336310</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>306815</t>
+          <t>336310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6376,17 +6376,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>306815</t>
+          <t>336310</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>306815</t>
+          <t>336310</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>306815</t>
+          <t>336310</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6423,32 +6423,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>249452</t>
+          <t>280289</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>239328</t>
+          <t>269054</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>256975</t>
+          <t>289520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6458,32 +6458,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>249452</t>
+          <t>280289</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239328</t>
+          <t>269054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>256975</t>
+          <t>289520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -6501,32 +6501,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26689</t>
+          <t>28762</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>19531</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36813</t>
+          <t>39997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6536,32 +6536,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>26689</t>
+          <t>28762</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>19531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36813</t>
+          <t>39997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -6579,17 +6579,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6614,17 +6614,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6661,32 +6661,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>102148</t>
+          <t>112427</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94961</t>
+          <t>104807</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108057</t>
+          <t>119067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6696,32 +6696,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>102148</t>
+          <t>112427</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94961</t>
+          <t>104807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108057</t>
+          <t>119067</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -6739,32 +6739,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>13017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23789</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6774,32 +6774,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>13017</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23789</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -6817,17 +6817,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>118750</t>
+          <t>132084</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>118750</t>
+          <t>132084</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118750</t>
+          <t>132084</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6852,17 +6852,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>118750</t>
+          <t>132084</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118750</t>
+          <t>132084</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118750</t>
+          <t>132084</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6899,32 +6899,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>547497</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222771</t>
+          <t>531892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>677276</t>
+          <t>560665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6934,32 +6934,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>547497</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>222771</t>
+          <t>531892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>677276</t>
+          <t>560665</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -6977,32 +6977,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>271906</t>
+          <t>74369</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84479</t>
+          <t>61201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>538984</t>
+          <t>89974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7012,32 +7012,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>271906</t>
+          <t>74369</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84479</t>
+          <t>61201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>538984</t>
+          <t>89974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -7055,17 +7055,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>761755</t>
+          <t>621866</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>761755</t>
+          <t>621866</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>761755</t>
+          <t>621866</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7090,17 +7090,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761755</t>
+          <t>621866</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761755</t>
+          <t>621866</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761755</t>
+          <t>621866</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7137,32 +7137,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>599860</t>
+          <t>550626</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>580001</t>
+          <t>532183</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>625050</t>
+          <t>566128</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7172,32 +7172,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>599860</t>
+          <t>550626</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>580001</t>
+          <t>532183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>625050</t>
+          <t>566128</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>87,15%</t>
         </is>
       </c>
     </row>
@@ -7215,32 +7215,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82510</t>
+          <t>98999</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57320</t>
+          <t>83497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102369</t>
+          <t>117442</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7250,32 +7250,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>82510</t>
+          <t>98999</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57320</t>
+          <t>83497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102369</t>
+          <t>117442</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -7293,17 +7293,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>682370</t>
+          <t>649625</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>682370</t>
+          <t>649625</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>682370</t>
+          <t>649625</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7328,17 +7328,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>682370</t>
+          <t>649625</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>682370</t>
+          <t>649625</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>682370</t>
+          <t>649625</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7375,32 +7375,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>454503</t>
+          <t>495724</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>428890</t>
+          <t>468776</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>479000</t>
+          <t>524492</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7410,32 +7410,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>454503</t>
+          <t>495724</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>428890</t>
+          <t>468776</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>479000</t>
+          <t>524492</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>
@@ -7453,32 +7453,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>162402</t>
+          <t>183541</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137905</t>
+          <t>154773</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188015</t>
+          <t>210489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7488,32 +7488,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>162402</t>
+          <t>183541</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137905</t>
+          <t>154773</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>188015</t>
+          <t>210489</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -7531,17 +7531,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>616905</t>
+          <t>679265</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>616905</t>
+          <t>679265</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>616905</t>
+          <t>679265</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7566,17 +7566,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>616905</t>
+          <t>679265</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>616905</t>
+          <t>679265</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>616905</t>
+          <t>679265</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7613,32 +7613,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2173326</t>
+          <t>2289727</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1734975</t>
+          <t>2245537</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2365160</t>
+          <t>2325439</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7648,32 +7648,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2173326</t>
+          <t>2289727</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1734975</t>
+          <t>2245537</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2365160</t>
+          <t>2325439</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -7691,32 +7691,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>589411</t>
+          <t>438474</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>397577</t>
+          <t>402762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1027762</t>
+          <t>482664</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7726,32 +7726,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>589411</t>
+          <t>438474</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>397577</t>
+          <t>402762</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1027762</t>
+          <t>482664</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -7769,17 +7769,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2762737</t>
+          <t>2728201</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2762737</t>
+          <t>2728201</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2762737</t>
+          <t>2728201</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7804,17 +7804,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2762737</t>
+          <t>2728201</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2762737</t>
+          <t>2728201</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2762737</t>
+          <t>2728201</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
